--- a/cet4/result/69_教育女神_支教女师的传奇/69_教育女神_支教女师的传奇_学习版.xlsx
+++ b/cet4/result/69_教育女神_支教女师的传奇/69_教育女神_支教女师的传奇_学习版.xlsx
@@ -397,563 +397,535 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D37"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>window</v>
       </c>
       <c r="B2" t="str">
-        <v>window</v>
+        <v>/ˈwɪndoʊ/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>窗户</v>
       </c>
-      <c r="D2" t="str">
-        <v>window(窗户)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>last</v>
       </c>
       <c r="B3" t="str">
-        <v>last</v>
+        <v>/læst/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D3" t="str">
         <v>最后</v>
       </c>
-      <c r="D3" t="str">
-        <v>last(最后)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>slightly</v>
       </c>
       <c r="B4" t="str">
-        <v>slightly</v>
+        <v>/ˈslaɪtli/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D4" t="str">
         <v>轻微</v>
       </c>
-      <c r="D4" t="str">
-        <v>slightly(轻微)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>lack</v>
       </c>
       <c r="B5" t="str">
-        <v>lack</v>
+        <v>/læk/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D5" t="str">
         <v>缺乏</v>
       </c>
-      <c r="D5" t="str">
-        <v>lack(缺乏)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>pursuit</v>
       </c>
       <c r="B6" t="str">
-        <v>pursuit</v>
+        <v>/pərˈsuːt/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>追求</v>
       </c>
-      <c r="D6" t="str">
-        <v>pursuit(追求)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>community</v>
       </c>
       <c r="B7" t="str">
-        <v>community</v>
+        <v>/kəˈmjuːnəti/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>社区</v>
       </c>
-      <c r="D7" t="str">
-        <v>community(社区)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>where</v>
       </c>
       <c r="B8" t="str">
-        <v>where</v>
+        <v>/wer/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./v./adv./pron./conj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>哪里</v>
       </c>
-      <c r="D8" t="str">
-        <v>where(哪里)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>block</v>
       </c>
       <c r="B9" t="str">
-        <v>block</v>
+        <v>/blɑːk/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>块</v>
       </c>
-      <c r="D9" t="str">
-        <v>block(块)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>flat</v>
       </c>
       <c r="B10" t="str">
-        <v>flat</v>
+        <v>/flæt/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D10" t="str">
         <v>平坦</v>
       </c>
-      <c r="D10" t="str">
-        <v>flat(平坦)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>speech</v>
       </c>
       <c r="B11" t="str">
-        <v>speech</v>
+        <v>/spiːtʃ/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>演讲</v>
       </c>
-      <c r="D11" t="str">
-        <v>speech(演讲)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>typical</v>
       </c>
       <c r="B12" t="str">
-        <v>typical</v>
+        <v>/ˈtɪpɪkl/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>典型</v>
       </c>
-      <c r="D12" t="str">
-        <v>typical(典型)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>pronounce</v>
       </c>
       <c r="B13" t="str">
-        <v>pronounce</v>
+        <v>/prəˈnaʊns/</v>
       </c>
       <c r="C13" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D13" t="str">
         <v>发音</v>
       </c>
-      <c r="D13" t="str">
-        <v>pronounce(发音)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>limited</v>
       </c>
       <c r="B14" t="str">
-        <v>limited</v>
+        <v>/ˈlɪmɪtɪd/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>有限</v>
       </c>
-      <c r="D14" t="str">
-        <v>limited(有限)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>cattle</v>
       </c>
       <c r="B15" t="str">
-        <v>cattle</v>
+        <v>/ˈkætl/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>牛</v>
       </c>
-      <c r="D15" t="str">
-        <v>cattle(牛)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>themselves</v>
       </c>
       <c r="B16" t="str">
-        <v>themselves</v>
+        <v>/ðəmˈselvz/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D16" t="str">
         <v>他们自己</v>
       </c>
-      <c r="D16" t="str">
-        <v>themselves(他们自己)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>composition</v>
       </c>
       <c r="B17" t="str">
-        <v>composition</v>
+        <v>/ˌkɑːmpəˈzɪʃn/</v>
       </c>
       <c r="C17" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>作文</v>
       </c>
-      <c r="D17" t="str">
-        <v>composition(作文)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>rider</v>
       </c>
       <c r="B18" t="str">
-        <v>rider</v>
+        <v>/ˈraɪdər/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>骑手</v>
       </c>
-      <c r="D18" t="str">
-        <v>rider(骑手)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>however</v>
       </c>
       <c r="B19" t="str">
-        <v>however</v>
+        <v>/haʊˈevər/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./adv./conj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>然而</v>
       </c>
-      <c r="D19" t="str">
-        <v>however(然而)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>resident</v>
       </c>
       <c r="B20" t="str">
-        <v>resident</v>
+        <v>/ˈrezɪdənt/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>居民</v>
       </c>
-      <c r="D20" t="str">
-        <v>resident(居民)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>interaction</v>
       </c>
       <c r="B21" t="str">
-        <v>interaction</v>
+        <v>/ˌɪntərˈækʃn/</v>
       </c>
       <c r="C21" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>互动</v>
       </c>
-      <c r="D21" t="str">
-        <v>interaction(互动)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>delicious</v>
       </c>
       <c r="B22" t="str">
-        <v>delicious</v>
+        <v>/dɪˈlɪʃəs/</v>
       </c>
       <c r="C22" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>美味</v>
       </c>
-      <c r="D22" t="str">
-        <v>delicious(美味)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>uncomfortable</v>
       </c>
       <c r="B23" t="str">
-        <v>slightly</v>
+        <v>/ʌnˈkʌmftəbl/</v>
       </c>
       <c r="C23" t="str">
-        <v>稍微</v>
+        <v>adj.</v>
       </c>
       <c r="D23" t="str">
-        <v>slightly(稍微)📢</v>
+        <v>不舒服</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>investment</v>
       </c>
       <c r="B24" t="str">
-        <v>uncomfortable</v>
+        <v>/ɪnˈvestmənt/</v>
       </c>
       <c r="C24" t="str">
-        <v>不舒服</v>
+        <v>n.</v>
       </c>
       <c r="D24" t="str">
-        <v>uncomfortable(不舒服)📢</v>
+        <v>投入</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>yield</v>
       </c>
       <c r="B25" t="str">
-        <v>investment</v>
+        <v>/jiːld/</v>
       </c>
       <c r="C25" t="str">
-        <v>投入</v>
+        <v>n./v.</v>
       </c>
       <c r="D25" t="str">
-        <v>investment(投入)📢</v>
+        <v>产出</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>mistress</v>
       </c>
       <c r="B26" t="str">
-        <v>yield</v>
+        <v>/ˈmɪstrəs/</v>
       </c>
       <c r="C26" t="str">
-        <v>产出</v>
+        <v>n.</v>
       </c>
       <c r="D26" t="str">
-        <v>yield(产出)📢</v>
+        <v>女主人</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>conscience</v>
       </c>
       <c r="B27" t="str">
-        <v>mistress</v>
+        <v>/ˈkɑːnʃəns/</v>
       </c>
       <c r="C27" t="str">
-        <v>女主人</v>
+        <v>n.</v>
       </c>
       <c r="D27" t="str">
-        <v>mistress(女主人)📢</v>
+        <v>良心</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>wisdom</v>
       </c>
       <c r="B28" t="str">
-        <v>conscience</v>
+        <v>/ˈwɪzdəm/</v>
       </c>
       <c r="C28" t="str">
-        <v>良心</v>
+        <v>n.</v>
       </c>
       <c r="D28" t="str">
-        <v>conscience(良心)📢</v>
+        <v>智慧</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>square</v>
       </c>
       <c r="B29" t="str">
-        <v>wisdom</v>
+        <v>/skwer/</v>
       </c>
       <c r="C29" t="str">
-        <v>智慧</v>
+        <v>n./vt./vi./v./adj./adv.</v>
       </c>
       <c r="D29" t="str">
-        <v>wisdom(智慧)📢</v>
+        <v>广场</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>static</v>
       </c>
       <c r="B30" t="str">
-        <v>square</v>
+        <v>/ˈstætɪk/</v>
       </c>
       <c r="C30" t="str">
-        <v>广场</v>
+        <v>n./adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>square(广场)📢</v>
+        <v>静态</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>route</v>
       </c>
       <c r="B31" t="str">
-        <v>static</v>
+        <v>/ruːt,raʊt/</v>
       </c>
       <c r="C31" t="str">
-        <v>静态</v>
+        <v>n./v.</v>
       </c>
       <c r="D31" t="str">
-        <v>static(静态)📢</v>
+        <v>路线</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>recall</v>
       </c>
       <c r="B32" t="str">
-        <v>route</v>
+        <v>/rɪˈkɔːl/</v>
       </c>
       <c r="C32" t="str">
-        <v>路线</v>
+        <v>n./vt.</v>
       </c>
       <c r="D32" t="str">
-        <v>route(路线)📢</v>
+        <v>回忆</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>root</v>
       </c>
       <c r="B33" t="str">
-        <v>recall</v>
+        <v>/ruːt/</v>
       </c>
       <c r="C33" t="str">
-        <v>回忆</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>recall(回忆)📢</v>
+        <v>根</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>century</v>
       </c>
       <c r="B34" t="str">
-        <v>pursuit</v>
+        <v>/ˈsentʃəri/</v>
       </c>
       <c r="C34" t="str">
-        <v>追求</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>pursuit(追求)📢</v>
+        <v>世纪</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>whole</v>
       </c>
       <c r="B35" t="str">
-        <v>root</v>
+        <v>/hoʊl/</v>
       </c>
       <c r="C35" t="str">
-        <v>根</v>
+        <v>n./adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>root(根)📢</v>
+        <v>整体</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>rusty</v>
       </c>
       <c r="B36" t="str">
-        <v>century</v>
+        <v>/ˈrʌsti/</v>
       </c>
       <c r="C36" t="str">
-        <v>世纪</v>
+        <v>adj.</v>
       </c>
       <c r="D36" t="str">
-        <v>century(世纪)📢</v>
+        <v>生锈</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>thirdly</v>
       </c>
       <c r="B37" t="str">
-        <v>whole</v>
+        <v>/ˈθɜːrdli/</v>
       </c>
       <c r="C37" t="str">
-        <v>整体</v>
+        <v>v./adv.</v>
       </c>
       <c r="D37" t="str">
-        <v>whole(整体)📢</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>rusty</v>
-      </c>
-      <c r="C38" t="str">
-        <v>生锈</v>
-      </c>
-      <c r="D38" t="str">
-        <v>rusty(生锈)📢</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>thirdly</v>
-      </c>
-      <c r="C39" t="str">
         <v>第三</v>
-      </c>
-      <c r="D39" t="str">
-        <v>thirdly(第三)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D37"/>
   </ignoredErrors>
 </worksheet>
 </file>